--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2101-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2101-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B852F040-D646-4EE1-A3D5-4551B7328768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B52C5B3F-0807-4D25-8448-B521F24BF910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A3C38C04-F562-40AC-9FBF-38B42BCF7F75}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{94E371CA-88BE-49D1-ACD3-537F988FA744}"/>
   </bookViews>
   <sheets>
     <sheet name="2101-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1487,23 +1487,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B8BAEB-09C3-41A3-A901-4F5B4384DD28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A424D881-84C9-442E-8A11-B7DD8B4D6BB9}">
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1657,7 +1657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2020</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2019</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2018</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2017</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2016</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2015</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2014</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2013</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2012</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2011</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2010</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2009</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2008</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2007</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2006</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2005</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2004</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2003</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2002</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2001</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2000</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1999</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>1998</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>1997</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>1996</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>1995</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>1994</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>1993</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>1992</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>1991</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>1984</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
         <v>47</v>
       </c>
